--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M627"/>
+  <dimension ref="A1:M632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28639,6 +28639,231 @@
         <v>372.75</v>
       </c>
       <c r="M627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="C628" t="n">
+        <v>384.63</v>
+      </c>
+      <c r="D628" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="E628" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="F628" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="G628" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="H628" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="I628" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="J628" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="K628" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="L628" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="C629" t="n">
+        <v>384.99</v>
+      </c>
+      <c r="D629" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="E629" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="F629" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="G629" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="H629" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="I629" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="J629" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="K629" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="L629" t="n">
+        <v>372.96</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="C630" t="n">
+        <v>385.09</v>
+      </c>
+      <c r="D630" t="n">
+        <v>375.93</v>
+      </c>
+      <c r="E630" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="F630" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="G630" t="n">
+        <v>386.66</v>
+      </c>
+      <c r="H630" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="I630" t="n">
+        <v>378.48</v>
+      </c>
+      <c r="J630" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="K630" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="L630" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="C631" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="D631" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="E631" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="F631" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="G631" t="n">
+        <v>386.42</v>
+      </c>
+      <c r="H631" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="I631" t="n">
+        <v>378.28</v>
+      </c>
+      <c r="J631" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="K631" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="L631" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="C632" t="n">
+        <v>384.98</v>
+      </c>
+      <c r="D632" t="n">
+        <v>375.34</v>
+      </c>
+      <c r="E632" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="F632" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="G632" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="H632" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="I632" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="J632" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="K632" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="L632" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="M632" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28655,7 +28880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35238,6 +35463,56 @@
       </c>
       <c r="B658" t="n">
         <v>-0.9</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -35406,28 +35681,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3267635794677538</v>
+        <v>-0.3317224332010411</v>
       </c>
       <c r="J2" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K2" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2951479023988701</v>
+        <v>0.303999337496149</v>
       </c>
       <c r="M2" t="n">
-        <v>2.957277383067852</v>
+        <v>2.957953186662134</v>
       </c>
       <c r="N2" t="n">
-        <v>14.41888662522511</v>
+        <v>14.38546955159706</v>
       </c>
       <c r="O2" t="n">
-        <v>3.797220908141257</v>
+        <v>3.792818154301239</v>
       </c>
       <c r="P2" t="n">
-        <v>384.8784147157718</v>
+        <v>384.9308815785151</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35484,28 +35759,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1376314593478921</v>
+        <v>-0.1363863600616893</v>
       </c>
       <c r="J3" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K3" t="n">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05832092254628796</v>
+        <v>0.05827339082555882</v>
       </c>
       <c r="M3" t="n">
-        <v>3.219049795364196</v>
+        <v>3.200028030814179</v>
       </c>
       <c r="N3" t="n">
-        <v>17.43651367945407</v>
+        <v>17.30263784783825</v>
       </c>
       <c r="O3" t="n">
-        <v>4.175705171519425</v>
+        <v>4.15964395685956</v>
       </c>
       <c r="P3" t="n">
-        <v>387.9308446920414</v>
+        <v>387.917703155925</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35562,28 +35837,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1353011224188677</v>
+        <v>-0.135817749720413</v>
       </c>
       <c r="J4" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K4" t="n">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1335877339615655</v>
+        <v>0.1365153668912957</v>
       </c>
       <c r="M4" t="n">
-        <v>1.877813263942854</v>
+        <v>1.865823043289284</v>
       </c>
       <c r="N4" t="n">
-        <v>6.750112890527091</v>
+        <v>6.697718084571467</v>
       </c>
       <c r="O4" t="n">
-        <v>2.598097937054547</v>
+        <v>2.587994993150386</v>
       </c>
       <c r="P4" t="n">
-        <v>379.4582137380589</v>
+        <v>379.463670305557</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35640,28 +35915,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01926119003218254</v>
+        <v>-0.01984248566957173</v>
       </c>
       <c r="J5" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K5" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002905491547314565</v>
+        <v>0.00313732037692549</v>
       </c>
       <c r="M5" t="n">
-        <v>1.894715033846054</v>
+        <v>1.882763143967272</v>
       </c>
       <c r="N5" t="n">
-        <v>7.208916053715328</v>
+        <v>7.15280971034197</v>
       </c>
       <c r="O5" t="n">
-        <v>2.684942467487028</v>
+        <v>2.674473725864954</v>
       </c>
       <c r="P5" t="n">
-        <v>379.4617887395671</v>
+        <v>379.467936217778</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35718,28 +35993,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01120414693928377</v>
+        <v>0.009321429148848539</v>
       </c>
       <c r="J6" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K6" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0007103857461217</v>
+        <v>0.0004999821735304222</v>
       </c>
       <c r="M6" t="n">
-        <v>2.367715503746154</v>
+        <v>2.358303691424321</v>
       </c>
       <c r="N6" t="n">
-        <v>9.998658945897914</v>
+        <v>9.931191254661009</v>
       </c>
       <c r="O6" t="n">
-        <v>3.162065613787594</v>
+        <v>3.151379262269302</v>
       </c>
       <c r="P6" t="n">
-        <v>380.1970936905626</v>
+        <v>380.2170067206209</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35796,28 +36071,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05057426751437265</v>
+        <v>0.05042370209283896</v>
       </c>
       <c r="J7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01420950687695766</v>
+        <v>0.01437365882094221</v>
       </c>
       <c r="M7" t="n">
-        <v>2.420822347855201</v>
+        <v>2.404019188377113</v>
       </c>
       <c r="N7" t="n">
-        <v>10.03392761797879</v>
+        <v>9.955240765883108</v>
       </c>
       <c r="O7" t="n">
-        <v>3.167637545234427</v>
+        <v>3.155192666998817</v>
       </c>
       <c r="P7" t="n">
-        <v>385.4057654182293</v>
+        <v>385.4073617566876</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35874,28 +36149,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01334776905985332</v>
+        <v>0.01375546655386442</v>
       </c>
       <c r="J8" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K8" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001209908566695783</v>
+        <v>0.001307610307240581</v>
       </c>
       <c r="M8" t="n">
-        <v>2.140347462255217</v>
+        <v>2.125258694687825</v>
       </c>
       <c r="N8" t="n">
-        <v>8.316587926311747</v>
+        <v>8.251661373906833</v>
       </c>
       <c r="O8" t="n">
-        <v>2.883849497860758</v>
+        <v>2.872570516785764</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2642804953739</v>
+        <v>382.2599693057059</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35952,28 +36227,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04246556894723467</v>
+        <v>-0.04185287667264231</v>
       </c>
       <c r="J9" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K9" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01052801711813722</v>
+        <v>0.0104087681813132</v>
       </c>
       <c r="M9" t="n">
-        <v>2.434972176854963</v>
+        <v>2.41806832740928</v>
       </c>
       <c r="N9" t="n">
-        <v>9.583782637190531</v>
+        <v>9.50921072369653</v>
       </c>
       <c r="O9" t="n">
-        <v>3.095768505103463</v>
+        <v>3.083700816177946</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1731308517332</v>
+        <v>379.1666503991712</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36030,28 +36305,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09629211438800039</v>
+        <v>-0.09540663423116282</v>
       </c>
       <c r="J10" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K10" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03595020993074804</v>
+        <v>0.03591695238315173</v>
       </c>
       <c r="M10" t="n">
-        <v>3.002562893560476</v>
+        <v>2.982984714740287</v>
       </c>
       <c r="N10" t="n">
-        <v>14.06000974526442</v>
+        <v>13.9511323624339</v>
       </c>
       <c r="O10" t="n">
-        <v>3.749667951334414</v>
+        <v>3.735121465552881</v>
       </c>
       <c r="P10" t="n">
-        <v>381.7697507489356</v>
+        <v>381.760382848604</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36108,28 +36383,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2100437447217812</v>
+        <v>-0.2109673700751143</v>
       </c>
       <c r="J11" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K11" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1570314388225982</v>
+        <v>0.1604762072450296</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88256809667541</v>
+        <v>2.866675299727738</v>
       </c>
       <c r="N11" t="n">
-        <v>13.3921533766376</v>
+        <v>13.29505924713294</v>
       </c>
       <c r="O11" t="n">
-        <v>3.659529119523112</v>
+        <v>3.646239055126931</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4732298311714</v>
+        <v>380.4829894247039</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36186,28 +36461,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3118291933932131</v>
+        <v>-0.3170109250337549</v>
       </c>
       <c r="J12" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="K12" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2518617559472673</v>
+        <v>0.2604903769912353</v>
       </c>
       <c r="M12" t="n">
-        <v>3.178344900200268</v>
+        <v>3.178691493907711</v>
       </c>
       <c r="N12" t="n">
-        <v>16.33274996984612</v>
+        <v>16.29063247746511</v>
       </c>
       <c r="O12" t="n">
-        <v>4.041379711168714</v>
+        <v>4.036165566161168</v>
       </c>
       <c r="P12" t="n">
-        <v>384.4805377867774</v>
+        <v>384.5353602646769</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36245,7 +36520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M627"/>
+  <dimension ref="A1:M632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78209,6 +78484,341 @@
         </is>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-36.770203742658566,174.77264897921066</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-36.76512403009603,174.76783168161091</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-36.76581260922292,174.76812145008222</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-36.766435742032584,174.7685609076737</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-36.767058277918665,174.7689973337287</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-36.767616758968195,174.76950688634943</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-36.76815546340301,174.77005520098095</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-36.76870707086773,174.7706250232283</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>-36.76919196696928,174.77125313671468</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>-36.76963283018798,174.77195579134903</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>-36.7701523493417,174.77259412972683</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-36.770205632786556,174.77264556472042</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-36.76512256506869,174.76783527949001</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-36.76581106406714,174.7681252486703</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-36.766436256408554,174.76855972529322</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-36.76705954933569,174.76899462454384</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-36.767620176257196,174.76950125082388</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-36.768159468607244,174.77004988780243</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-36.768709293061534,174.7706222408425</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>-36.7691925313455,174.77125257908378</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>-36.769632058624865,174.77195656500916</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>-36.7701560537517,174.7725895460424</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.770209668464894,174.77263827432182</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.76512215811665,174.76783627890083</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.76580931560123,174.7681295470724</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.76643569916792,174.7685610062054</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.76706045749068,174.7689926894117</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-36.76761995928648,174.76950160863504</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-36.7681579281441,174.7700519313327</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-36.768708404184025,174.77062335379682</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>-36.7691928135336,174.77125230026832</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>-36.76963416288789,174.77195445502684</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>-36.770159119470186,174.77258575264807</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.770209668464894,174.77263827432182</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.76512057100354,174.76784017660296</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.76581082009517,174.7681258484473</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.76643582776192,174.76856071061027</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.767061365645624,174.76899075427954</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-36.76762126111079,174.76949946176808</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-36.76815909889609,174.7700503782497</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-36.76870967400902,174.77062176386204</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>-36.76919203751631,174.7712530670108</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>-36.76962041503559,174.77196824024256</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>-36.770159119470186,174.77258575264807</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.77021099666274,174.77263587494994</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.765122605763914,174.7678351795489</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.765811714659066,174.7681236492648</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.766436213543884,174.76855982382492</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.767061365645624,174.76899075427954</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-36.76762136959614,174.76949928286248</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-36.76815903727757,174.77005045999093</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-36.768709293061534,174.7706222408425</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-36.76919175532821,174.77125334582627</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>-36.76962041503559,174.77196824024256</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>-36.77015982203064,174.7725848833285</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0167/nzd0167.xlsx
+++ b/data/nzd0167/nzd0167.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M632"/>
+  <dimension ref="A1:M636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28858,12 +28858,192 @@
         <v>379.82</v>
       </c>
       <c r="K632" t="n">
-        <v>375.31</v>
+        <v>375.04</v>
       </c>
       <c r="L632" t="n">
         <v>372.37</v>
       </c>
       <c r="M632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="C633" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="D633" t="n">
+        <v>375.67</v>
+      </c>
+      <c r="E633" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="F633" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="G633" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="H633" t="n">
+        <v>382.99</v>
+      </c>
+      <c r="I633" t="n">
+        <v>378.56</v>
+      </c>
+      <c r="J633" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="K633" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="L633" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="C634" t="n">
+        <v>385.77</v>
+      </c>
+      <c r="D634" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="E634" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="F634" t="n">
+        <v>379.57</v>
+      </c>
+      <c r="G634" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="H634" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="I634" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="J634" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="K634" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="L634" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="C635" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="D635" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="E635" t="n">
+        <v>379.05</v>
+      </c>
+      <c r="F635" t="n">
+        <v>379.48</v>
+      </c>
+      <c r="G635" t="n">
+        <v>387.23</v>
+      </c>
+      <c r="H635" t="n">
+        <v>383.43</v>
+      </c>
+      <c r="I635" t="n">
+        <v>378.94</v>
+      </c>
+      <c r="J635" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="K635" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="L635" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="C636" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="D636" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="E636" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="F636" t="n">
+        <v>379.1</v>
+      </c>
+      <c r="G636" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="H636" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="I636" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="J636" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="K636" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="L636" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="M636" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28880,7 +29060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B663"/>
+  <dimension ref="A1:B667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35513,6 +35693,46 @@
       </c>
       <c r="B663" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -35681,28 +35901,28 @@
         <v>0.0446</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3317224332010411</v>
+        <v>-0.3348713183582384</v>
       </c>
       <c r="J2" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.303999337496149</v>
+        <v>0.310387252644078</v>
       </c>
       <c r="M2" t="n">
-        <v>2.957953186662134</v>
+        <v>2.954654995516598</v>
       </c>
       <c r="N2" t="n">
-        <v>14.38546955159706</v>
+        <v>14.33561222281431</v>
       </c>
       <c r="O2" t="n">
-        <v>3.792818154301239</v>
+        <v>3.786239852784596</v>
       </c>
       <c r="P2" t="n">
-        <v>384.9308815785151</v>
+        <v>384.9643235115057</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35759,28 +35979,28 @@
         <v>0.0502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1363863600616893</v>
+        <v>-0.1346244243161605</v>
       </c>
       <c r="J3" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K3" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05827339082555882</v>
+        <v>0.05757250433420746</v>
       </c>
       <c r="M3" t="n">
-        <v>3.200028030814179</v>
+        <v>3.189073888438878</v>
       </c>
       <c r="N3" t="n">
-        <v>17.30263784783825</v>
+        <v>17.20559446938437</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15964395685956</v>
+        <v>4.147962689005817</v>
       </c>
       <c r="P3" t="n">
-        <v>387.917703155925</v>
+        <v>387.8990333301081</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35837,28 +36057,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.135817749720413</v>
+        <v>-0.1357579584511198</v>
       </c>
       <c r="J4" t="n">
+        <v>635</v>
+      </c>
+      <c r="K4" t="n">
         <v>631</v>
       </c>
-      <c r="K4" t="n">
-        <v>627</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1365153668912957</v>
+        <v>0.138059193052216</v>
       </c>
       <c r="M4" t="n">
-        <v>1.865823043289284</v>
+        <v>1.854711391393727</v>
       </c>
       <c r="N4" t="n">
-        <v>6.697718084571467</v>
+        <v>6.65537885159399</v>
       </c>
       <c r="O4" t="n">
-        <v>2.587994993150386</v>
+        <v>2.579802095431739</v>
       </c>
       <c r="P4" t="n">
-        <v>379.463670305557</v>
+        <v>379.4630355384774</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35915,28 +36135,28 @@
         <v>0.06510000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01984248566957173</v>
+        <v>-0.02000628987202723</v>
       </c>
       <c r="J5" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00313732037692549</v>
+        <v>0.003233685589109081</v>
       </c>
       <c r="M5" t="n">
-        <v>1.882763143967272</v>
+        <v>1.872116517954616</v>
       </c>
       <c r="N5" t="n">
-        <v>7.15280971034197</v>
+        <v>7.108046553253011</v>
       </c>
       <c r="O5" t="n">
-        <v>2.674473725864954</v>
+        <v>2.666092000147971</v>
       </c>
       <c r="P5" t="n">
-        <v>379.467936217778</v>
+        <v>379.4696764943711</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35993,28 +36213,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009321429148848539</v>
+        <v>0.007940739999786773</v>
       </c>
       <c r="J6" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0004999821735304222</v>
+        <v>0.0003676864334103414</v>
       </c>
       <c r="M6" t="n">
-        <v>2.358303691424321</v>
+        <v>2.350315591664451</v>
       </c>
       <c r="N6" t="n">
-        <v>9.931191254661009</v>
+        <v>9.876571707579778</v>
       </c>
       <c r="O6" t="n">
-        <v>3.151379262269302</v>
+        <v>3.142701339227095</v>
       </c>
       <c r="P6" t="n">
-        <v>380.2170067206209</v>
+        <v>380.2316668433543</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36071,28 +36291,28 @@
         <v>0.083</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05042370209283896</v>
+        <v>0.0507324605474646</v>
       </c>
       <c r="J7" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K7" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01437365882094221</v>
+        <v>0.01474838144474167</v>
       </c>
       <c r="M7" t="n">
-        <v>2.404019188377113</v>
+        <v>2.390261096806782</v>
       </c>
       <c r="N7" t="n">
-        <v>9.955240765883108</v>
+        <v>9.893127022865938</v>
       </c>
       <c r="O7" t="n">
-        <v>3.155192666998817</v>
+        <v>3.145334167122142</v>
       </c>
       <c r="P7" t="n">
-        <v>385.4073617566876</v>
+        <v>385.4040823986107</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36149,28 +36369,28 @@
         <v>0.1004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01375546655386442</v>
+        <v>0.01437893828399812</v>
       </c>
       <c r="J8" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K8" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001307610307240581</v>
+        <v>0.001448402640654267</v>
       </c>
       <c r="M8" t="n">
-        <v>2.125258694687825</v>
+        <v>2.114700032803841</v>
       </c>
       <c r="N8" t="n">
-        <v>8.251661373906833</v>
+        <v>8.201509253774123</v>
       </c>
       <c r="O8" t="n">
-        <v>2.872570516785764</v>
+        <v>2.863827727670455</v>
       </c>
       <c r="P8" t="n">
-        <v>382.2599693057059</v>
+        <v>382.2533477170572</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36227,28 +36447,28 @@
         <v>0.1127</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04185287667264231</v>
+        <v>-0.04102626994902306</v>
       </c>
       <c r="J9" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K9" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0104087681813132</v>
+        <v>0.01014187055437632</v>
       </c>
       <c r="M9" t="n">
-        <v>2.41806832740928</v>
+        <v>2.406013924739451</v>
       </c>
       <c r="N9" t="n">
-        <v>9.50921072369653</v>
+        <v>9.452308658266933</v>
       </c>
       <c r="O9" t="n">
-        <v>3.083700816177946</v>
+        <v>3.074460710151771</v>
       </c>
       <c r="P9" t="n">
-        <v>379.1666503991712</v>
+        <v>379.1578715636799</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36305,28 +36525,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09540663423116282</v>
+        <v>-0.09388979234479354</v>
       </c>
       <c r="J10" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K10" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03591695238315173</v>
+        <v>0.03527256916111021</v>
       </c>
       <c r="M10" t="n">
-        <v>2.982984714740287</v>
+        <v>2.971363152866382</v>
       </c>
       <c r="N10" t="n">
-        <v>13.9511323624339</v>
+        <v>13.87277133324253</v>
       </c>
       <c r="O10" t="n">
-        <v>3.735121465552881</v>
+        <v>3.724616937786023</v>
       </c>
       <c r="P10" t="n">
-        <v>381.760382848604</v>
+        <v>381.7442722703227</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36383,28 +36603,28 @@
         <v>0.0667</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2109673700751143</v>
+        <v>-0.2103218647618977</v>
       </c>
       <c r="J11" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K11" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1604762072450296</v>
+        <v>0.1615153532017096</v>
       </c>
       <c r="M11" t="n">
-        <v>2.866675299727738</v>
+        <v>2.852462291812033</v>
       </c>
       <c r="N11" t="n">
-        <v>13.29505924713294</v>
+        <v>13.21323283057867</v>
       </c>
       <c r="O11" t="n">
-        <v>3.646239055126931</v>
+        <v>3.635001077108323</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4829894247039</v>
+        <v>380.4761305290261</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36461,28 +36681,28 @@
         <v>0.0464</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3170109250337549</v>
+        <v>-0.3199637106641139</v>
       </c>
       <c r="J12" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K12" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2604903769912353</v>
+        <v>0.2663634715201428</v>
       </c>
       <c r="M12" t="n">
-        <v>3.178691493907711</v>
+        <v>3.173101188992431</v>
       </c>
       <c r="N12" t="n">
-        <v>16.29063247746511</v>
+        <v>16.22432611596862</v>
       </c>
       <c r="O12" t="n">
-        <v>4.036165566161168</v>
+        <v>4.027943161958547</v>
       </c>
       <c r="P12" t="n">
-        <v>384.5353602646769</v>
+        <v>384.5667167881838</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36520,7 +36740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M632"/>
+  <dimension ref="A1:M636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78805,7 +79025,7 @@
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>-36.76962041503559,174.77196824024256</t>
+          <t>-36.76962230887248,174.77196634125906</t>
         </is>
       </c>
       <c r="L632" t="inlineStr">
@@ -78814,6 +79034,274 @@
         </is>
       </c>
       <c r="M632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.77020680773092,174.7726434421994</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.76512053030833,174.76784027654404</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.76581037281319,174.76812694803857</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.76643527052127,174.7685619915224</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.76706045749068,174.7689926894117</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-36.767619199888934,174.76950286097411</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-36.76815755843295,174.77005242177995</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-36.768707896254014,174.77062398977074</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>-36.76918886290006,174.77125620368452</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>-36.76962090603034,174.7719677479135</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>-36.77015515958377,174.77259065244905</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.77020481543391,174.7726470412568</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.76511939084243,174.7678430748942</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.76580943758724,174.76812924718385</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.766434498957295,174.76856376509303</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.76705891362719,174.76899597913626</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-36.76761724715236,174.76950608127436</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-36.76815626444388,174.77005413834527</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-36.768706181990204,174.77062613618259</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>-36.769186887583245,174.7712581553925</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>-36.76961985389873,174.7719688029043</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>-36.7701523493417,174.77259412972683</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.77020496868754,174.7726467644062</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.76511902458552,174.76784397436387</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.765808949643244,174.7681304467379</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.76643389885196,174.7685651445368</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-36.76705932229695,174.76899510832683</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-36.76761686745357,174.76950670744387</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-36.76815484721774,174.77005601839295</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-36.76870548358641,174.77062701064665</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>-36.769186464301065,174.77125857361563</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>-36.769619433046074,174.77196922490063</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>-36.77015068874406,174.77259618448176</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.77020471326483,174.77264722582382</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.76512020474665,174.76784107607267</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.76580984420722,174.7681282475555</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.766436213543884,174.76855982382492</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.7670610477914,174.7689914315758</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-36.76761871170479,174.7695036660492</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-36.7681579281441,174.7700519313327</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-36.76870821371026,174.77062359228705</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>-36.769187875241656,174.7712571795385</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>-36.76961929276186,174.77196936556606</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>-36.770150113921815,174.77259689574308</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
